--- a/04-advanced-analysis/05-statistics-forecasting/4.5-statistics-forecasting.xlsx
+++ b/04-advanced-analysis/05-statistics-forecasting/4.5-statistics-forecasting.xlsx
@@ -64482,7 +64482,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="51" customHeight="1">
+    <row r="8" ht="81" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B3</t>
@@ -64495,7 +64495,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Compare each month's rate with its own limits. A helper column of UCL and LCL, then COUNTIFS, works</t>
+          <t>Compare each month's rate with its own limits. Helper columns for the rate, UCL, LCL, and a TRUE/FALSE flag, then COUNTIF the flags, works. So does one SUMPRODUCT</t>
         </is>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -64863,7 +64863,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="126" customHeight="1">
+    <row r="13" ht="171" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -64888,7 +64888,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>217 patients saw a provider. Their mean wait was 49.15 minutes with a standard deviation of 45.52. The margin is t × s ÷ √n = 1.9710 × 45.52 ÷ √217 = 6.09, so the 95% confidence interval is 43.1 to 55.2 minutes. Use COUNT, not ROWS or COUNTA: the 9 blank rows aren't measurements, and counting them gives 5.97. CONFIDENCE.NORM (and the old CONFIDENCE) uses 1.96 instead of t and gives 6.06, slightly too narrow. The ToolPak's "Confidence Level(95.0%)" row is CONFIDENCE.T.</t>
+          <t>217 patients saw a provider. Their mean wait was 49.15 minutes with a standard deviation of 45.52. The margin is t × s ÷ √n = 1.9710 × 45.52 ÷ √217 = 6.09, so the 95% confidence interval is 43.1 to 55.2 minutes. Use COUNT, not ROWS: ROWS also counts the 9 blank rows, which aren't measurements, and gives 5.97. COUNTA agrees with COUNT here only because the blank cells are truly empty. It would also count a text entry such as "LWBS" if an export had one. CONFIDENCE.NORM (and the old CONFIDENCE) uses 1.96 instead of t and gives 6.06, slightly too narrow. The ToolPak's "Confidence Level(95.0%)" row is CONFIDENCE.T.</t>
         </is>
       </c>
     </row>

--- a/04-advanced-analysis/05-statistics-forecasting/4.5-statistics-forecasting.xlsx
+++ b/04-advanced-analysis/05-statistics-forecasting/4.5-statistics-forecasting.xlsx
@@ -1385,10 +1385,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="64" customHeight="1">
+    <row r="2" ht="79" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Stays (rows 2–401) holds the 400 sampled inpatient stays: Bluestone Memorial in rows 2–201 and Cedar Ridge in rows 202–401. Bins (A4:A10) holds the LOS histogram bins. EDWaits holds Q4 2025 ED visits sorted by hospital. EDDaily holds one row per day from 01/01/2024 (row 2) to 12/31/2025 (row 732), with 2025 starting in row 368. Monthly holds Jan 2024 (row 2) to Dec 2025 (row 25). Answer with formulas where you can. Where a task says the ToolPak, a worksheet formula gives the same number.</t>
+          <t>Stays (rows 2–401) holds the 400 sampled inpatient stays: Bluestone Memorial in rows 2–201 and Cedar Ridge in rows 202–401. Bins (A4:A10) holds the LOS histogram bins. EDWaits holds Q4 2025 ED visits sorted by hospital. EDDaily holds one row per day from 01/01/2024 (row 2) to 12/31/2025 (row 732), with 2025 starting in row 368. Monthly holds Jan 2024 (row 2) to Dec 2025 (row 25). Answer with formulas where you can. Where a task says the ToolPak, a worksheet formula gives the same number. Each yellow cell holds one number, so wrap FREQUENCY or LINEST in INDEX there. Otherwise they spill into the cells below.</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Build a histogram of LOSDays (all 400 stays) using the bins on the Bins sheet, with the Histogram tool or FREQUENCY. How many stays fall in the bin labeled 6?</t>
+          <t>Build a histogram of LOSDays (all 400 stays) using the bins on the Bins sheet, with the Histogram tool or FREQUENCY. How many stays fall in the bin labeled 6? Enter that one count.</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Is the age effect from Task 5 real, or could it be chance? Run Regression (Data Analysis) with LOSDays as the Y range and Age as the X range, or use LINEST. What p-value does it report for the Age coefficient? Enter it to 4 decimal places.</t>
+          <t>Is the age effect from Task 5 real, or could it be chance? Run Regression (Data Analysis) with LOSDays as the Y range and Age as the X range, or build the p-value from LINEST as in guide section 7. What p-value does it report for the Age coefficient? Enter it to 4 decimal places.</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Build an individuals (I) chart for Memorial's daily arrivals with 2024 as the baseline (EDDaily rows 2–367). The moving ranges are the absolute day-to-day changes, sigma = average moving range ÷ 1.128, and UCL = mean + 3 × sigma. What is the UCL? Enter it to 2 decimal places.</t>
+          <t>Build an individuals (I) chart for Memorial's daily arrivals with 2024 as the baseline (EDDaily rows 2–367). The moving ranges are the absolute day-to-day changes, σ̂ = average moving range ÷ 1.128, and UCL = mean + 3 × σ̂. What is the UCL? Enter it to 2 decimal places.</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -64391,10 +64391,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="64" customHeight="1">
+    <row r="2" ht="79" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>The quality committee wants a p-chart of Bluestone's system-wide 30-day readmission rate by discharge month, January 2024 to December 2025 (Monthly sheet, rows 2–25). For each month, n = IndexStays (inpatient discharges of patients who didn't die) and the rate = Readmits30 ÷ IndexStays. The center line p̄ = total readmissions ÷ total index stays, and each month gets its own limits: p̄ ± 3 × √(p̄ × (1 − p̄) ÷ n). Your B1 answer lands in cell D6 of this sheet, so later parts can refer to it. Helper columns to the right of the Monthly table make this much easier.</t>
+          <t>The quality committee wants a p-chart of Bluestone's system-wide 30-day readmission rate by discharge month, January 2024 to December 2025 (Monthly sheet, rows 2–25). For each month, n = IndexStays (inpatient discharges of patients who didn't die) and the rate = Readmits30 ÷ IndexStays. The center line p̄ = total readmissions ÷ total index stays, and each month gets its own limits: p̄ ± 3 × √(p̄ × (1 − p̄) ÷ n). Your B1 answer lands in cell D6 of this sheet, so later parts can refer to it. Helper columns for each month's rate, UCL, and LCL make this much easier. Put them in empty columns to the right of the Monthly table.</t>
         </is>
       </c>
     </row>
@@ -64495,7 +64495,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Compare each month's rate with its own limits. Helper columns for the rate, UCL, LCL, and a TRUE/FALSE flag, then COUNTIF the flags, works. So does one SUMPRODUCT</t>
+          <t>Compare each month's rate with its own limits. Add helper columns for the rate, UCL, LCL, and a TRUE/FALSE flag, then COUNTIF the flags. One SUMPRODUCT also works</t>
         </is>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -64668,7 +64668,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Build a histogram of LOSDays (all 400 stays) using the bins on the Bins sheet, with the Histogram tool or FREQUENCY. How many stays fall in the bin labeled 6?</t>
+          <t>Build a histogram of LOSDays (all 400 stays) using the bins on the Bins sheet, with the Histogram tool or FREQUENCY. How many stays fall in the bin labeled 6? Enter that one count.</t>
         </is>
       </c>
       <c r="C6" s="43" t="n">
@@ -64784,7 +64784,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Is the age effect from Task 5 real, or could it be chance? Run Regression (Data Analysis) with LOSDays as the Y range and Age as the X range, or use LINEST. What p-value does it report for the Age coefficient? Enter it to 4 decimal places.</t>
+          <t>Is the age effect from Task 5 real, or could it be chance? Run Regression (Data Analysis) with LOSDays as the Y range and Age as the X range, or build the p-value from LINEST as in guide section 7. What p-value does it report for the Age coefficient? Enter it to 4 decimal places.</t>
         </is>
       </c>
       <c r="C10" s="49" t="n">
@@ -64958,7 +64958,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Build an individuals (I) chart for Memorial's daily arrivals with 2024 as the baseline (EDDaily rows 2–367). The moving ranges are the absolute day-to-day changes, sigma = average moving range ÷ 1.128, and UCL = mean + 3 × sigma. What is the UCL? Enter it to 2 decimal places.</t>
+          <t>Build an individuals (I) chart for Memorial's daily arrivals with 2024 as the baseline (EDDaily rows 2–367). The moving ranges are the absolute day-to-day changes, σ̂ = average moving range ÷ 1.128, and UCL = mean + 3 × σ̂. What is the UCL? Enter it to 2 decimal places.</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
@@ -64975,7 +64975,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>2024 averaged 11.773 arrivals a day. The 365 moving ranges average 4.148, so sigma = 4.148 ÷ 1.128 = 3.677 and UCL = 11.773 + 3 × 3.677 = 22.80. The LCL is 0.74. Many references write this as mean ± 2.66 × MR̄, which is the same thing, because 3 ÷ 1.128 ≈ 2.66. A helper column of =ABS(C3-C2) filled down and averaged works too. The moving range measures short-term, day-to-day noise, so a slow seasonal swing doesn't widen the limits the way STDEV.S does (it would put the UCL at 23.35).</t>
+          <t>2024 averaged 11.773 arrivals a day. The 365 moving ranges average 4.148, so σ̂ = 4.148 ÷ 1.128 = 3.677 and UCL = 11.773 + 3 × 3.677 = 22.80. The LCL is 0.74. Many references write this as mean ± 2.66 × MR̄, which is the same thing, because 3 ÷ 1.128 ≈ 2.66. A helper column of =ABS(C3-C2) filled down and averaged works too. The moving range measures short-term, day-to-day noise, so a slow seasonal swing doesn't widen the limits the way STDEV.S does (it would put the UCL at 23.35).</t>
         </is>
       </c>
     </row>

--- a/04-advanced-analysis/05-statistics-forecasting/4.5-statistics-forecasting.xlsx
+++ b/04-advanced-analysis/05-statistics-forecasting/4.5-statistics-forecasting.xlsx
@@ -801,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C33"/>
+  <dimension ref="B2:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -826,7 +826,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Advanced  ·  about 70 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Advanced  ·  about 150 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -1033,82 +1033,106 @@
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Stays</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Data: 400 rows, in the Excel Table 'tblStays'</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Bins</t>
+          <t>Stays</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 7 rows, in the Excel Table 'tblBins'</t>
+          <t>Data: 400 rows, in the Excel Table 'tblStays'</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>EDWaits</t>
+          <t>Bins</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 1,628 rows, in the Excel Table 'tblEDWaits'</t>
+          <t>Data: 7 rows, in the Excel Table 'tblBins'</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>EDDaily</t>
+          <t>EDWaits</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 731 rows, in the Excel Table 'tblEDDaily'</t>
+          <t>Data: 1,628 rows, in the Excel Table 'tblEDWaits'</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
+          <t>EDDaily</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Data: 731 rows, in the Excel Table 'tblEDDaily'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Data: 24 rows, in the Excel Table 'tblMonthly'</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="63" customHeight="1">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>A random sample of 400 inpatient stays discharged in 2025 (200 each from Bluestone Memorial and Cedar Ridge), every Q4 2025 emergency department visit at the three hospitals with door-to-provider minutes, daily ED arrivals per hospital for 2024–2025, and 24 months of system-wide ED, LWBS, inpatient, and 30-day readmission counts.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="63" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>A random sample of 400 inpatient stays discharged in 2025 (200 each from Bluestone Memorial and Cedar Ridge), every Q4 2025 emergency department visit at the three hospitals with door-to-provider minutes, daily ED arrivals per hospital for 2024–2025, and 24 months of system-wide ED, LWBS, inpatient, and 30-day readmission counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/04-advanced-analysis/05-statistics-forecasting/4.5-statistics-forecasting.xlsx
+++ b/04-advanced-analysis/05-statistics-forecasting/4.5-statistics-forecasting.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Run Data Analysis → Descriptive Statistics on LOSDays for all 400 stays (tick Summary statistics). What Skewness does the output report? Enter it to 2 decimal places, or use the worksheet function that calculates it.</t>
+          <t>Run Data → Data Analysis → Descriptive Statistics on LOSDays for all 400 stays (tick Summary statistics). What Skewness does the output report? Enter it to 2 decimal places, or use the worksheet function that calculates it.</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Is the age effect from Task 5 real, or could it be chance? Run Regression (Data Analysis) with LOSDays as the Y range and Age as the X range, or build the p-value from LINEST as in guide section 7. What p-value does it report for the Age coefficient? Enter it to 4 decimal places.</t>
+          <t>Is the age effect from Task 5 real, or could it be chance? Run Data → Data Analysis → Regression with LOSDays as the Y range and Age as the X range, or build the p-value from LINEST as in guide section 7. What p-value does it report for the Age coefficient? Enter it to 4 decimal places.</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
@@ -64395,7 +64395,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>The quality committee wants a p-chart of Bluestone's system-wide 30-day readmission rate by discharge month, January 2024 to December 2025 (Monthly sheet, rows 2–25). For each month, n = IndexStays (inpatient discharges of patients who didn't die) and the rate = Readmits30 ÷ IndexStays. The center line p̄ = total readmissions ÷ total index stays, and each month gets its own limits: p̄ ± 3 × √(p̄ × (1 − p̄) ÷ n). Your B1 answer lands in cell D6 of this sheet, so later parts can refer to it. Helper columns for each month's rate, UCL, and LCL make this much easier. Put them in empty columns to the right of the Monthly table.</t>
+          <t>The quality committee wants a p-chart of Bluestone's system-wide 30-day readmission rate by discharge month, January 2024 to December 2025 (Monthly sheet, rows 2–25). For each month, n = IndexStays (inpatient discharges of patients who didn't die) and the rate = Readmits30 ÷ IndexStays. The center line p̄ = total readmissions ÷ total index stays, and each month gets its own limits: p̄ ± 3 × √(p̄ × (1 − p̄) ÷ n). Your B1 answer lands in cell D6 of the Bonus sheet, so later parts can refer to it. Helper columns for each month's rate, UCL, and LCL make this much easier. Put them in empty columns to the right of the Monthly Table.</t>
         </is>
       </c>
     </row>
@@ -64640,7 +64640,7 @@
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>Run Data Analysis → Descriptive Statistics on LOSDays for all 400 stays (tick Summary statistics). What Skewness does the output report? Enter it to 2 decimal places, or use the worksheet function that calculates it.</t>
+          <t>Run Data → Data Analysis → Descriptive Statistics on LOSDays for all 400 stays (tick Summary statistics). What Skewness does the output report? Enter it to 2 decimal places, or use the worksheet function that calculates it.</t>
         </is>
       </c>
       <c r="C5" s="39" t="n">
@@ -64785,7 +64785,7 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Is the age effect from Task 5 real, or could it be chance? Run Regression (Data Analysis) with LOSDays as the Y range and Age as the X range, or build the p-value from LINEST as in guide section 7. What p-value does it report for the Age coefficient? Enter it to 4 decimal places.</t>
+          <t>Is the age effect from Task 5 real, or could it be chance? Run Data → Data Analysis → Regression with LOSDays as the Y range and Age as the X range, or build the p-value from LINEST as in guide section 7. What p-value does it report for the Age coefficient? Enter it to 4 decimal places.</t>
         </is>
       </c>
       <c r="C10" s="47" t="n">
